--- a/taxonomies/AMT Taxonomy - Job Function.xlsx
+++ b/taxonomies/AMT Taxonomy - Job Function.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Taxonomy Metadata" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Release Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Hierarchy &amp; Mapping" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Look-up values" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxonomy Metadata" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hierarchy &amp; Mapping" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Look-up values" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Management, Corporate and Executive</t>
+          <t>Finance/HR Department</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Management, Design or R&amp;D</t>
+          <t>Management, Corporate and Executive</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Management, Manufacturing Engineering</t>
+          <t>Management, Design or R&amp;D</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Management, Manufacturing Production</t>
+          <t>Management, Manufacturing Engineering</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other (Please specify)</t>
+          <t>Management, Manufacturing Production</t>
         </is>
       </c>
     </row>
@@ -875,6 +875,18 @@
         </is>
       </c>
       <c r="B14" t="inlineStr">
+        <is>
+          <t>Other (Please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JF13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>No Response</t>
         </is>
